--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/FAROL - 24_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/FAROL - 24_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CARENAGEM FAROL BRANCO MELC BRIS NXR160 2022 A 2024</t>
+          <t>CARENAGEM FAROL BRANCO MELC BROS NXR160 2022 A 2024</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -499,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,7 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -596,7 +584,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLOCO OPTICO MELC CB250 TWISTER 2016 A 2020 807000</t>
+          <t>BLOCO OPTICO MELC CBX250 TWISTER 2016 A 2020 807000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -604,7 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -625,7 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -646,7 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -667,7 +652,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -688,11 +672,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -709,7 +688,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -730,7 +708,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -747,7 +724,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -768,11 +744,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -793,7 +764,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -801,22 +771,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7898667940554</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CG TITAN150 2014 EM DIANTE</t>
+          <t>BLOCO OPTICO CG TITAN150 2014 EM DIANTE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
     </row>
@@ -839,11 +804,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -864,11 +824,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -889,11 +844,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -914,7 +864,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -935,11 +884,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -960,7 +904,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -981,7 +924,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1002,7 +944,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1023,7 +964,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1044,7 +984,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1065,7 +1004,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
